--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518983</v>
+        <v>124518962</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767506</v>
+        <v>767494</v>
       </c>
       <c r="R3" t="n">
-        <v>7072805</v>
+        <v>7072810</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,12 +887,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518962</v>
+        <v>124518983</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767494</v>
+        <v>767506</v>
       </c>
       <c r="R4" t="n">
-        <v>7072810</v>
+        <v>7072805</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +994,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518983</v>
+        <v>124518974</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767506</v>
+        <v>767413</v>
       </c>
       <c r="R4" t="n">
-        <v>7072805</v>
+        <v>7072907</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518974</v>
+        <v>124518983</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767413</v>
+        <v>767506</v>
       </c>
       <c r="R5" t="n">
-        <v>7072907</v>
+        <v>7072805</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518962</v>
+        <v>124518974</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767494</v>
+        <v>767413</v>
       </c>
       <c r="R3" t="n">
-        <v>7072810</v>
+        <v>7072907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,12 +886,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -910,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518974</v>
+        <v>124518983</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767413</v>
+        <v>767506</v>
       </c>
       <c r="R4" t="n">
-        <v>7072907</v>
+        <v>7072805</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1032,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518983</v>
+        <v>124518962</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767506</v>
+        <v>767494</v>
       </c>
       <c r="R5" t="n">
-        <v>7072805</v>
+        <v>7072810</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,6 +1115,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518974</v>
+        <v>124518983</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767413</v>
+        <v>767506</v>
       </c>
       <c r="R3" t="n">
-        <v>7072907</v>
+        <v>7072805</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518983</v>
+        <v>124518974</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767506</v>
+        <v>767413</v>
       </c>
       <c r="R4" t="n">
-        <v>7072805</v>
+        <v>7072907</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518974</v>
+        <v>124518962</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767413</v>
+        <v>767494</v>
       </c>
       <c r="R4" t="n">
-        <v>7072907</v>
+        <v>7072810</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,12 +1009,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518962</v>
+        <v>124518974</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767494</v>
+        <v>767413</v>
       </c>
       <c r="R5" t="n">
-        <v>7072810</v>
+        <v>7072907</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1116,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518962</v>
+        <v>124518983</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767494</v>
+        <v>767506</v>
       </c>
       <c r="R3" t="n">
-        <v>7072810</v>
+        <v>7072805</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,12 +886,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -910,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518983</v>
+        <v>124518962</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767506</v>
+        <v>767494</v>
       </c>
       <c r="R4" t="n">
-        <v>7072805</v>
+        <v>7072810</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518983</v>
+        <v>124518962</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767506</v>
+        <v>767494</v>
       </c>
       <c r="R3" t="n">
-        <v>7072805</v>
+        <v>7072810</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,6 +871,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,12 +887,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518962</v>
+        <v>124518974</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767494</v>
+        <v>767413</v>
       </c>
       <c r="R4" t="n">
-        <v>7072810</v>
+        <v>7072907</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +994,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518974</v>
+        <v>124518983</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767413</v>
+        <v>767506</v>
       </c>
       <c r="R5" t="n">
-        <v>7072907</v>
+        <v>7072805</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518962</v>
+        <v>124518974</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767494</v>
+        <v>767413</v>
       </c>
       <c r="R3" t="n">
-        <v>7072810</v>
+        <v>7072907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,12 +886,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -910,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518974</v>
+        <v>124518962</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767413</v>
+        <v>767494</v>
       </c>
       <c r="R4" t="n">
-        <v>7072907</v>
+        <v>7072810</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518974</v>
+        <v>124518983</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767413</v>
+        <v>767506</v>
       </c>
       <c r="R3" t="n">
-        <v>7072907</v>
+        <v>7072805</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518962</v>
+        <v>124518974</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767494</v>
+        <v>767413</v>
       </c>
       <c r="R4" t="n">
-        <v>7072810</v>
+        <v>7072907</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,12 +1008,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518983</v>
+        <v>124518962</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767506</v>
+        <v>767494</v>
       </c>
       <c r="R5" t="n">
-        <v>7072805</v>
+        <v>7072810</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,6 +1115,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124518983</v>
+        <v>124518974</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767506</v>
+        <v>767413</v>
       </c>
       <c r="R3" t="n">
-        <v>7072805</v>
+        <v>7072907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124518974</v>
+        <v>124518962</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767413</v>
+        <v>767494</v>
       </c>
       <c r="R4" t="n">
-        <v>7072907</v>
+        <v>7072810</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,12 +1009,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1031,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124518962</v>
+        <v>124518983</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767494</v>
+        <v>767506</v>
       </c>
       <c r="R5" t="n">
-        <v>7072810</v>
+        <v>7072805</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1116,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,6 +1152,342 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125424542</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>112</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bastuskäret, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>767499</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7072803</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125424544</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bastuskäret, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>767491</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7072836</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125424543</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bastuskäret, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>767493</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7072826</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125424542</v>
+        <v>125424543</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,25 +1166,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767499</v>
+        <v>767493</v>
       </c>
       <c r="R6" t="n">
-        <v>7072803</v>
+        <v>7072826</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125424544</v>
+        <v>125424542</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767491</v>
+        <v>767499</v>
       </c>
       <c r="R7" t="n">
-        <v>7072836</v>
+        <v>7072803</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125424543</v>
+        <v>125424544</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,25 +1390,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767493</v>
+        <v>767491</v>
       </c>
       <c r="R8" t="n">
-        <v>7072826</v>
+        <v>7072836</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125424543</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125424542</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>91116</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>125424544</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>91162</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125424543</v>
+        <v>125424542</v>
       </c>
       <c r="B6" t="n">
-        <v>91131</v>
+        <v>91116</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,25 +1166,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767493</v>
+        <v>767499</v>
       </c>
       <c r="R6" t="n">
-        <v>7072826</v>
+        <v>7072803</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125424542</v>
+        <v>125424544</v>
       </c>
       <c r="B7" t="n">
-        <v>91116</v>
+        <v>91162</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>767499</v>
+        <v>767491</v>
       </c>
       <c r="R7" t="n">
-        <v>7072803</v>
+        <v>7072836</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125424544</v>
+        <v>125424543</v>
       </c>
       <c r="B8" t="n">
-        <v>91162</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,25 +1390,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767491</v>
+        <v>767493</v>
       </c>
       <c r="R8" t="n">
-        <v>7072836</v>
+        <v>7072826</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -1154,37 +1154,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125424542</v>
+        <v>125424543</v>
       </c>
       <c r="B6" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>767499</v>
+        <v>767493</v>
       </c>
       <c r="R6" t="n">
-        <v>7072803</v>
+        <v>7072826</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,12 +1264,7 @@
         <v>125424544</v>
       </c>
       <c r="B7" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,37 +1368,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125424543</v>
+        <v>125424542</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1418,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>767493</v>
+        <v>767499</v>
       </c>
       <c r="R8" t="n">
-        <v>7072826</v>
+        <v>7072803</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1453,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125424543</v>
       </c>
       <c r="B6" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>125424544</v>
       </c>
       <c r="B7" t="n">
-        <v>91216</v>
+        <v>91223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>125424542</v>
       </c>
       <c r="B8" t="n">
-        <v>91170</v>
+        <v>91177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125424543</v>
       </c>
       <c r="B6" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>125424544</v>
       </c>
       <c r="B7" t="n">
-        <v>91223</v>
+        <v>91224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>125424542</v>
       </c>
       <c r="B8" t="n">
-        <v>91177</v>
+        <v>91178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 11796-2025 artfynd.xlsx
+++ b/artfynd/A 11796-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125424543</v>
       </c>
       <c r="B6" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>125424544</v>
       </c>
       <c r="B7" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>125424542</v>
       </c>
       <c r="B8" t="n">
-        <v>91178</v>
+        <v>91182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
